--- a/templates/template_input4.xlsx
+++ b/templates/template_input4.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="안내" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="인원표" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="안내" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="연간근무표" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -586,14 +586,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>입력④ 인원표 — 양식 안내</t>
+          <t>입력④ 연간근무표 — 양식 안내</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="20" t="inlineStr">
         <is>
-          <t>다월 자동 연동용 파일입니다. 지난달 생성 후 받은 '인원표'를 그대로 다시 올리면, 인원 명단과 누적 통계(야간·근무일·OFF 등 형평성 지표)가 이번 달 생성에 자동으로 이어집니다.</t>
+          <t>다월 자동 연동용 파일입니다. 지난달 생성 후 받은 '연간근무표'를 그대로 다시 올리면, 인원 명단과 누적 통계(야간·근무일·OFF 등 형평성 지표)가 이번 달 생성에 자동으로 이어집니다.</t>
         </is>
       </c>
     </row>
@@ -641,7 +641,7 @@
     <row r="11">
       <c r="A11" s="20" t="inlineStr">
         <is>
-          <t>이 파일 없이 생략해도 됩니다 — 입력①②③만으로 근무표 생성이 가능하고, 이 앱이 매달 자동으로 인원표를 만들어 드리니 다음 달부터 이어받으면 됩니다.</t>
+          <t>이 파일 없이 생략해도 됩니다 — 입력①②③만으로 근무표 생성이 가능하고, 이 앱이 매달 자동으로 연간근무표를 만들어 드리니 다음 달부터 이어받으면 됩니다.</t>
         </is>
       </c>
     </row>
@@ -712,7 +712,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>인원표 — 2026년 9월까지 반영</t>
+          <t>연간근무표 — 2026년 9월까지 반영</t>
         </is>
       </c>
     </row>
